--- a/results/Int Task Remove ACC -0.1/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7230240734160944</v>
+        <v>0.7135247244878777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7227064114084705</v>
+        <v>0.7224802833023463</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.723163342739344</v>
+        <v>0.7131984504196288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7267272594848315</v>
+        <v>0.7165581382988671</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7242555980854651</v>
+        <v>0.7048782156204079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.736300918193298</v>
+        <v>0.727702882924203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.753407669359863</v>
+        <v>0.7431118278532741</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.753407669359863</v>
+        <v>0.7363752279735477</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7506574693139977</v>
+        <v>0.7363752279735477</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7652745967833215</v>
+        <v>0.7260488751664589</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7649788340155725</v>
+        <v>0.719143232839608</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7870805803446203</v>
+        <v>0.7243650942848396</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7931857931510988</v>
+        <v>0.7357969896172998</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7890475749913634</v>
+        <v>0.7518154223797436</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8005272057455731</v>
+        <v>0.7695011500791817</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.781736673697389</v>
+        <v>0.7705018715238032</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7443770625885198</v>
+        <v>0.7683478721320607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7626324165835807</v>
+        <v>0.7689135614856838</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7661485979073185</v>
+        <v>0.7639874628082011</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7574058800197241</v>
+        <v>0.7660937267781938</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7662268446295681</v>
+        <v>0.7794746544595218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7516793518218692</v>
+        <v>0.7859797129378741</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7559701264841041</v>
+        <v>0.7926811263984757</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7567447198226014</v>
+        <v>0.7953397925428414</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7484722204451304</v>
+        <v>0.791984779782228</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7484722204451304</v>
+        <v>0.7923117920271019</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5747708945814882</v>
+        <v>0.7601363953555895</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5800929019888447</v>
+        <v>0.7468078782146361</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5800929019888447</v>
+        <v>0.6678057552186627</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5789051757992238</v>
+        <v>0.6692766951734075</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5424335911702265</v>
+        <v>0.6966933132024367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.544857517147843</v>
+        <v>0.6909495608833317</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5410150617558565</v>
+        <v>0.6903533602292087</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.571981571174498</v>
+        <v>0.6777908243661277</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5471726851027099</v>
+        <v>0.6482037210007313</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5650493544891473</v>
+        <v>0.6282013489931764</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5636785604965271</v>
+        <v>0.6282013489931764</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6166427333400917</v>
+        <v>0.6467610778166113</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.618857755332834</v>
+        <v>0.6552816045400816</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6275871860411785</v>
+        <v>0.6555530074792055</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6246672053715636</v>
+        <v>0.6555530074792055</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5811765452743409</v>
+        <v>0.6555530074792055</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6053195960303814</v>
+        <v>0.6538645514789615</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6010593326686463</v>
+        <v>0.6571757657598249</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.599109562143153</v>
+        <v>0.6455701528616156</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.599109562143153</v>
+        <v>0.647697577894858</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5853366626739513</v>
+        <v>0.6482374310666061</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5858327173659496</v>
+        <v>0.6405220089821332</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5469160456960858</v>
+        <v>0.6324670256501613</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.545436493680716</v>
+        <v>0.6297864602659208</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5201925755179293</v>
+        <v>0.5635798908876525</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5143353900574498</v>
+        <v>0.566030391223769</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5128386139208301</v>
+        <v>0.55286697958794</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5153712979211962</v>
+        <v>0.5614837153315348</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.498282509052506</v>
+        <v>0.5697616280042559</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.488848119667289</v>
+        <v>0.594587000020669</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4827515189214354</v>
+        <v>0.5951910745587918</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4964626576130123</v>
+        <v>0.6187425997793343</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4961755069058884</v>
+        <v>0.6644044833895496</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4951747854612669</v>
+        <v>0.664582876073924</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5003489114847488</v>
+        <v>0.6643348487279248</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4993474518635023</v>
+        <v>0.6284702913435504</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4953571150876412</v>
+        <v>0.6298715966366705</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5014623278941199</v>
+        <v>0.603126965395264</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5026633412629907</v>
+        <v>0.5916559467016792</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4986205939467548</v>
+        <v>0.6106561209113627</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4938556638323965</v>
+        <v>0.5985177905487802</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4938556638323965</v>
+        <v>0.5995271240540267</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4938556638323965</v>
+        <v>0.6124690827023563</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4897260577332859</v>
+        <v>0.5472147611703347</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4981245392547566</v>
+        <v>0.5798485655259705</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4993951872852521</v>
+        <v>0.5987173442964044</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5013316706314953</v>
+        <v>0.5391863521968628</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5011532779471209</v>
+        <v>0.5435209253388477</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5019192592249933</v>
+        <v>0.5386863605628647</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5066669652181016</v>
+        <v>0.5361849260396234</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.507432946495974</v>
+        <v>0.5340833371882557</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.507432946495974</v>
+        <v>0.5340833371882557</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5035294685029876</v>
+        <v>0.5340833371882557</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5038471305106116</v>
+        <v>0.5321773651425123</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5038471305106116</v>
+        <v>0.5310937218570162</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5095392104659666</v>
+        <v>0.5417775982094788</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5101440231807145</v>
+        <v>0.530294030513269</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5107402238348374</v>
+        <v>0.5142458246269501</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5172898189695645</v>
+        <v>0.4727881029549702</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5172898189695645</v>
+        <v>0.4766829688873316</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5049785092178576</v>
+        <v>0.5012179914312457</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5015319625557446</v>
+        <v>0.498289398701006</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5016798439396191</v>
+        <v>0.4893080037046624</v>
       </c>
     </row>
   </sheetData>
